--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -660,49 +660,49 @@
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 175975억 × 비례계수 0.0022 × 계절비중 Q1 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 175974억 × 비례계수 0.0022 × 계절비중 Q1 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 176874억 × 비례계수 0.0022 × 계절비중 Q2 0.266(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 177426억 × 비례계수 0.0022 × 계절비중 Q2 0.266(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 176007억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 176545억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 174525억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 175051억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 172755억 × 비례계수 0.0022 × 계절비중 Q1 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 173268억 × 비례계수 0.0022 × 계절비중 Q1 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 171215억 × 비례계수 0.0022 × 계절비중 Q2 0.266(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 171162억 × 비례계수 0.0022 × 계절비중 Q2 0.266(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 168767억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 168714억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 165622억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 165569억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -930,7 +930,7 @@
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 -117억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -118억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
@@ -1809,49 +1809,49 @@
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 175975억 × 비례계수 0.0022 × 계절비중 Q1 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 175974억 × 비례계수 0.0022 × 계절비중 Q1 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 176874억 × 비례계수 0.0022 × 계절비중 Q2 0.266(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 177426억 × 비례계수 0.0022 × 계절비중 Q2 0.266(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 176007억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 176545억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 174525억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 175051억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 172755억 × 비례계수 0.0022 × 계절비중 Q1 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 173268억 × 비례계수 0.0022 × 계절비중 Q1 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 171215억 × 비례계수 0.0022 × 계절비중 Q2 0.266(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 171162억 × 비례계수 0.0022 × 계절비중 Q2 0.266(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 168767억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 168714억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 165622억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 165569억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2294,7 +2294,7 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 -117억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -118억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -6490,26 +6490,26 @@
         <v>0.401229</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.604988</v>
+        <v>0.609954</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.086187</v>
+        <v>0.08949799999999999</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.016946</v>
+        <v>0.020008</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.018268</v>
+        <v>-0.015336</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.032009</v>
+        <v>-0.035284</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.041093</v>
+        <v>-0.044321</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.050994</v>
+        <v>-0.054143</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6639,29 +6639,29 @@
         <v>0.231055</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.231022</v>
+        <v>0.231081</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.231004</v>
+        <v>0.231035</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.231078</v>
+        <v>0.231085</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.231105</v>
+        <v>0.231104</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.231069</v>
+        <v>0.231038</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.231039</v>
+        <v>0.231005</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.231013</v>
+        <v>0.231087</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6794,29 +6794,29 @@
         <v>-0.191249</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.191181</v>
+        <v>-0.191169</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.191172</v>
+        <v>-0.19122</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.191227</v>
+        <v>-0.191153</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.191247</v>
+        <v>-0.191251</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.191209</v>
+        <v>-0.191166</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.191144</v>
+        <v>-0.191207</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.191242</v>
+        <v>-0.191197</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7090,7 +7090,7 @@
         <v>-2.89</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>-2.99</v>
+        <v>-3</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AL32" s="29" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AL33" s="29" t="n">
         <v>0</v>
@@ -8433,26 +8433,26 @@
         <v>0.146018</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.148685</v>
+        <v>0.149122</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.12018</v>
+        <v>0.120451</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.112665</v>
+        <v>0.112991</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.089656</v>
+        <v>0.089777</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.09432599999999999</v>
+        <v>0.094276</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.079496</v>
+        <v>0.079376</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.076528</v>
+        <v>0.076422</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8561,26 +8561,26 @@
         <v>0.759115</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.503578</v>
+        <v>0.505058</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.310962</v>
+        <v>0.311475</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.249093</v>
+        <v>0.249625</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.176571</v>
+        <v>0.176653</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.172047</v>
+        <v>0.171725</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.135383</v>
+        <v>0.135167</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.123912</v>
+        <v>0.123674</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9517,29 +9517,29 @@
         <v>-0.191249</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>-0.191181</v>
+        <v>-0.191169</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>-0.191172</v>
+        <v>-0.19122</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>-0.191227</v>
+        <v>-0.191153</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ34,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>-0.191247</v>
+        <v>-0.191251</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>-0.191209</v>
+        <v>-0.191166</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>-0.191144</v>
+        <v>-0.191207</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>-0.191242</v>
+        <v>-0.191197</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO34,"")</f>
@@ -37775,7 +37775,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-1343.7</v>
+        <v>-1344.9</v>
       </c>
     </row>
     <row r="30">
@@ -37812,7 +37812,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-0.1666</v>
+        <v>-0.1668</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -648,61 +648,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 162049억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+전년동기 × (1+-12.7%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 171610억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+전년동기 × (1+-12.7%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 175974억 × 비례계수 0.0022 × 계절비중 Q1 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+전년동기 × (1+-12.7%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 177426억 × 비례계수 0.0022 × 계절비중 Q2 0.266(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+전년동기 × (1+-12.7%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 176545억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+전년동기 × (1+-6.3%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 175051억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+전년동기 × (1+-6.3%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 173268억 × 비례계수 0.0022 × 계절비중 Q1 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+전년동기 × (1+-6.3%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 171162억 × 비례계수 0.0022 × 계절비중 Q2 0.266(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+전년동기 × (1+-6.3%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 168714억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+전년동기 × (1+-3.2%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 165569억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)</t>
+전년동기 × (1+-3.2%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -768,121 +768,121 @@
     <comment ref="AC23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AD23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AG23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AH23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AI23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AK23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AL23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AM23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AN23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)</t>
+매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))</t>
       </text>
     </comment>
     <comment ref="AC24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -19.1% 유지</t>
+최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AD24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -19.1% 유지</t>
+최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AF24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -19.1% 유지</t>
+최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -19.1% 유지</t>
+최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AH24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -19.1% 유지</t>
+최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AI24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -19.1% 유지</t>
+최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AK24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -19.1% 유지</t>
+최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AL24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -19.1% 유지</t>
+최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AM24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -19.1% 유지</t>
+최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AN24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-최근 8분기 OPM 중위 -19.1% 유지</t>
+최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)</t>
       </text>
     </comment>
     <comment ref="AC25" authorId="0" shapeId="0">
@@ -894,55 +894,55 @@
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 -4억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 -23억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -10억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 -41억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -21억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 -61억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -33억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 -80억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -44억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 -100억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -55억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 -118억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -66억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 -138억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -77억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 -156억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 -88억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1797,61 +1797,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 162049억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 전년동기 × (1+-12.7%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 171610억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 전년동기 × (1+-12.7%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 175974억 × 비례계수 0.0022 × 계절비중 Q1 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 전년동기 × (1+-12.7%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 177426억 × 비례계수 0.0022 × 계절비중 Q2 0.266(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 전년동기 × (1+-12.7%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 176545억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 전년동기 × (1+-6.3%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 175051억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 전년동기 × (1+-6.3%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 173268억 × 비례계수 0.0022 × 계절비중 Q1 0.229(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 전년동기 × (1+-6.3%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 171162억 × 비례계수 0.0022 × 계절비중 Q2 0.266(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 전년동기 × (1+-6.3%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 168714억 × 비례계수 0.0022 × 계절비중 Q3 0.246(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 전년동기 × (1+-3.2%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 165569억 × 비례계수 0.0022 × 계절비중 Q4 0.259(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.75, n=16, 창 19)
+        <t>추정: 전년동기 × (1+-3.2%) — g=최근 4분기 합 YoY -12.7% 클립(−30~+50%), 연차별 절반 감쇠(가정)
 [yoy]</t>
       </text>
     </comment>
@@ -2037,61 +2037,61 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지)
+        <t>추정: 매출액 × OPM(최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%))
 [ratio]</t>
       </text>
     </comment>
@@ -2192,61 +2192,61 @@
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지
+        <t>추정: 최근 8분기 OPM 중위 -19.1% 유지(클립 −20~40%)
 [yoy]</t>
       </text>
     </comment>
@@ -2258,55 +2258,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 -4억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 -23억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -10억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 -41억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -21억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 -61억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -33억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 -80억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -44억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 -100억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -55억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 -118억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -66억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 -138억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -77억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 -156억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 -88억 × 2.24% − 총차입금 85억 × 9.98% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4304,7 +4304,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4425,14 +4425,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 OOS 기각 — 동결 2025Q2 이후 4분기 매출 WAPE 연동 32.3% &gt; 추세 20.9% × 1.10 (suppliers_mentions·시차 0·4분기 이동합·창 19, r=0.75 유의)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 20.0, "op_wape_pct": 43.6, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 87.78, "rev_act": 66.85, "op_pred": -17.56, "op_act": -9.23}, {"q": "2025Q4", "rev_pred": 86.28, "rev_act": 69.81, "op_pred": -17.26, "op_act": -13.47}, {"q": "2026Q1", "rev_pred": 67.84, "rev_act": 63.29, "op_pred": -13.57, "op_act": -10.33}, {"q": "2026Q2", "rev_pred": 75.23, "rev_act": 64.43, "op_pred": -15.05, "op_act": -11.14}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 32.3, "op_wape_pct": 58.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 7.6, "wape_trend": 9.9, "adopted": true}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 87.78, "rev_act": 66.85, "op_pred": -17.56, "op_act": -9.23}, {"q": "2025Q4", "rev_pred": 92.29, "rev_act": 69.81, "op_pred": -18.46, "op_act": -13.47}, {"q": "2026Q1", "rev_pred": 77.47, "rev_act": 63.29, "op_pred": -15.49, "op_act": -10.33}, {"q": "2026Q2", "rev_pred": 92.3, "rev_act": 64.43, "op_pred": -18.46, "op_act": -11.14}]}</t>
         </is>
       </c>
     </row>
@@ -6480,36 +6480,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.310373</v>
+        <v>-0.126717</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.403314</v>
+        <v>-0.126725</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.401229</v>
+        <v>-0.126681</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.609954</v>
+        <v>-0.12681</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.08949799999999999</v>
+        <v>-0.063378</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.020008</v>
+        <v>-0.06332</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.015336</v>
+        <v>-0.06350600000000001</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.035284</v>
+        <v>-0.063278</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.044321</v>
+        <v>-0.031639</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.054143</v>
+        <v>-0.031699</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6626,42 +6626,42 @@
         <v/>
       </c>
       <c r="AC22" s="24" t="n">
-        <v>0.23105</v>
+        <v>0.231072</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.231013</v>
+        <v>0.230971</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.231055</v>
+        <v>0.231048</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.231081</v>
+        <v>0.23107</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.231035</v>
+        <v>0.23098</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.231085</v>
+        <v>0.230998</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.231104</v>
+        <v>0.231066</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.231038</v>
+        <v>0.23112</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.231005</v>
+        <v>0.230973</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.231087</v>
+        <v>0.230964</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6781,42 +6781,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>-0.19121</v>
+        <v>-0.191161</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>-0.1912</v>
+        <v>-0.191109</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>-0.191249</v>
+        <v>-0.191243</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>-0.191169</v>
+        <v>-0.191255</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>-0.19122</v>
+        <v>-0.191112</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>-0.191153</v>
+        <v>-0.191243</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>-0.191251</v>
+        <v>-0.191267</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>-0.191166</v>
+        <v>-0.191271</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>-0.191207</v>
+        <v>-0.191124</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>-0.191197</v>
+        <v>-0.191174</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7058,39 +7058,39 @@
         <v>-2.05</v>
       </c>
       <c r="AD25" s="29" t="n">
-        <v>-2.14</v>
+        <v>-2.11</v>
       </c>
       <c r="AE25" s="30">
         <f>subQ!AE11</f>
         <v/>
       </c>
       <c r="AF25" s="29" t="n">
-        <v>-2.25</v>
+        <v>-2.18</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>-2.35</v>
+        <v>-2.24</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>-2.46</v>
+        <v>-2.3</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>-2.57</v>
+        <v>-2.36</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>-2.68</v>
+        <v>-2.43</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>-2.78</v>
+        <v>-2.49</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>-2.89</v>
+        <v>-2.55</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>-3</v>
+        <v>-2.61</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -8046,29 +8046,29 @@
       </c>
       <c r="AE32" s="30" t="n"/>
       <c r="AF32" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AG32" s="29" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AH32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AI32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AL32" s="29" t="n">
         <v>-0</v>
-      </c>
-      <c r="AL32" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AM32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -8174,29 +8174,29 @@
       </c>
       <c r="AE33" s="30" t="n"/>
       <c r="AF33" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AG33" s="29" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AH33" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AI33" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AL33" s="29" t="n">
         <v>-0</v>
-      </c>
-      <c r="AL33" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AM33" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AN33" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AO33" s="30" t="n"/>
     </row>
@@ -8423,36 +8423,36 @@
         <v/>
       </c>
       <c r="AC35" s="24" t="n">
-        <v>0.204516</v>
+        <v>0.137712</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.190538</v>
+        <v>0.126802</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.146018</v>
+        <v>0.1031</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.149122</v>
+        <v>0.095581</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.120451</v>
+        <v>0.08538800000000001</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.112991</v>
+        <v>0.082372</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.089777</v>
+        <v>0.069855</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.094276</v>
+        <v>0.066708</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.079376</v>
+        <v>0.06322800000000001</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.076422</v>
+        <v>0.062178</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -8551,36 +8551,36 @@
         <v/>
       </c>
       <c r="AC36" s="24" t="n">
-        <v>-1.292873</v>
+        <v>-0.870591</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>4.953488</v>
+        <v>-7.046784</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.759115</v>
+        <v>1.067698</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.505058</v>
+        <v>0.528064</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.311475</v>
+        <v>0.338231</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.249625</v>
+        <v>0.264639</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.176653</v>
+        <v>0.192078</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.171725</v>
+        <v>0.164618</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.135167</v>
+        <v>0.142913</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.123674</v>
+        <v>0.130742</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9203,36 +9203,36 @@
         <v/>
       </c>
       <c r="AC42" s="24" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="AD42" s="24" t="n">
-        <v>0.148148</v>
+        <v>0.111111</v>
       </c>
       <c r="AE42" s="25" t="n"/>
       <c r="AF42" s="24" t="n">
+        <v>0.107143</v>
+      </c>
+      <c r="AG42" s="24" t="n">
         <v>0.142857</v>
       </c>
-      <c r="AG42" s="24" t="n">
-        <v>0.214286</v>
-      </c>
       <c r="AH42" s="24" t="n">
-        <v>0.2</v>
+        <v>0.137931</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>0.225806</v>
+        <v>0.133333</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>0.25</v>
+        <v>0.129032</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>0.264706</v>
+        <v>0.125</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>0.277778</v>
+        <v>0.121212</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>0.289474</v>
+        <v>0.117647</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -9504,42 +9504,42 @@
         <v/>
       </c>
       <c r="AC44" s="24" t="n">
-        <v>-0.19121</v>
+        <v>-0.191161</v>
       </c>
       <c r="AD44" s="24" t="n">
-        <v>-0.1912</v>
+        <v>-0.191109</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE35/subQ!AE34,"")</f>
         <v/>
       </c>
       <c r="AF44" s="24" t="n">
-        <v>-0.191249</v>
+        <v>-0.191243</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>-0.191169</v>
+        <v>-0.191255</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>-0.19122</v>
+        <v>-0.191112</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>-0.191153</v>
+        <v>-0.191243</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ34,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>-0.191251</v>
+        <v>-0.191267</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>-0.191166</v>
+        <v>-0.191271</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>-0.191207</v>
+        <v>-0.191124</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>-0.191197</v>
+        <v>-0.191174</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO34,"")</f>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17768,7 +17768,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37775,7 +37775,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-1344.9</v>
+        <v>-831.5</v>
       </c>
     </row>
     <row r="30">
@@ -37812,7 +37812,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-0.1668</v>
+        <v>-0.1031</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4039,7 +4039,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4910,35 +4910,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5029,35 +5029,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5148,35 +5148,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5267,35 +5267,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5386,35 +5386,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5505,35 +5505,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5624,35 +5624,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5743,35 +5743,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9347,7 +9347,7 @@
         </is>
       </c>
       <c r="D53" s="34" t="n">
-        <v>0.0421538670116092</v>
+        <v>0.04215386701160923</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18021,7 +18021,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31466,7 +31466,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36471,7 +36471,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -4039,7 +4039,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4910,35 +4910,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5029,35 +5029,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5148,35 +5148,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5267,35 +5267,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5386,35 +5386,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5505,35 +5505,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5624,35 +5624,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5743,35 +5743,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18021,7 +18021,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31466,7 +31466,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36471,7 +36471,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -4039,7 +4039,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18021,7 +18021,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -4910,35 +4910,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5029,35 +5029,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5148,35 +5148,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5267,35 +5267,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5386,35 +5386,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5505,35 +5505,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5624,35 +5624,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5743,35 +5743,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -31466,7 +31466,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36471,7 +36471,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4910,35 +4910,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5029,35 +5029,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5148,35 +5148,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5267,35 +5267,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5386,35 +5386,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5505,35 +5505,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5624,35 +5624,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5743,35 +5743,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9347,7 +9347,7 @@
         </is>
       </c>
       <c r="D53" s="34" t="n">
-        <v>0.0421538670116092</v>
+        <v>0.04215386701160923</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>

--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -4039,7 +4039,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4910,35 +4910,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5029,35 +5029,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5148,35 +5148,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5267,35 +5267,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5386,35 +5386,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5505,35 +5505,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5624,35 +5624,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5743,35 +5743,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -4039,7 +4039,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -4039,7 +4039,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37041,7 +37041,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -4039,7 +4039,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4910,35 +4910,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5029,35 +5029,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5148,35 +5148,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5267,35 +5267,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5386,35 +5386,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5505,35 +5505,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5624,35 +5624,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5743,35 +5743,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37041,7 +37041,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -4039,7 +4039,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4910,35 +4910,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5029,35 +5029,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5148,35 +5148,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5267,35 +5267,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5386,35 +5386,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5505,35 +5505,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5624,35 +5624,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5743,35 +5743,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37041,7 +37041,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -4039,7 +4039,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4910,35 +4910,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5029,35 +5029,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5148,35 +5148,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5267,35 +5267,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5386,35 +5386,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5505,35 +5505,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5624,35 +5624,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5743,35 +5743,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37041,7 +37041,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/054180_model.xlsx
+++ b/argus/kship/models/054180_model.xlsx
@@ -4039,7 +4039,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4910,35 +4910,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5029,35 +5029,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5148,35 +5148,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5267,35 +5267,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5386,35 +5386,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5505,35 +5505,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5624,35 +5624,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5743,35 +5743,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32036,7 +32036,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37041,7 +37041,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
